--- a/data/BENEFICIOS - RELACAO.xlsx
+++ b/data/BENEFICIOS - RELACAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\NUCLEO\06 - OUTROS\08 - APLICAÇÕES\01 - IMPORTAR DADOS\01 - VERSÃO DESKTOP\Importar_Dados\DADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\06 - OUTROS\08 - APLICAÇÕES\IMPORTAR DADOS\Importar_Dados\DADOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573D2A27-D0CA-4EBE-9E6F-4F622ABFE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E0B972-4921-4CBB-8292-652B92DF68B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{73204379-9103-4EC7-9959-F9B57A8EF193}"/>
   </bookViews>
   <sheets>
     <sheet name="BENEFICIOS" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="86">
   <si>
     <t>VA</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>SUPERVISOR DE VIGILANCIA</t>
+  </si>
+  <si>
+    <t>INST.AMBIENTAL VALE</t>
   </si>
   <si>
     <t>INSTITUTO AMBIENTAL VALE</t>
@@ -267,7 +270,44 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>AMBIENTAL VALE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra)</t>
+    </r>
+  </si>
+  <si>
     <t>COZINHEIRO</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">AMBIENTAL VALE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(contém a palavra)</t>
+    </r>
   </si>
   <si>
     <t>AJUDANTE DE COZINHA</t>
@@ -294,6 +334,36 @@
     <t>4h</t>
   </si>
   <si>
+    <r>
+      <t>CESAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra, não brasilia)</t>
+    </r>
+  </si>
+  <si>
     <t>SIM</t>
   </si>
   <si>
@@ -313,6 +383,21 @@
   </si>
   <si>
     <t>GUIDONI TB2 - 5X2</t>
+  </si>
+  <si>
+    <r>
+      <t>GUIDONI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra)</t>
+    </r>
   </si>
   <si>
     <t>motorista RECEBE (VA + CB)</t>
@@ -341,6 +426,50 @@
   <si>
     <t>EX:
 ESC 05X02 - 14:00 AS 18:00 (não tem almoço é 4h)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra, não brasilia)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="0.39997558519241921"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CESAN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(contém a palavra)</t>
+    </r>
   </si>
   <si>
     <t>6h</t>
@@ -360,59 +489,12 @@
       <t xml:space="preserve"> (contém a palavra)</t>
     </r>
   </si>
-  <si>
-    <t>VALE SA</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT TRANSPORTE - GVBUS 1 P/DIA
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VT TRANSPORTE - GVBUS 2 P/DIA
-</t>
-  </si>
-  <si>
-    <r>
-      <t>CETURB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra)</t>
-    </r>
-  </si>
-  <si>
-    <t>SUPERVISOR(A)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">MULTILIFT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(contém a palavra)</t>
-    </r>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,12 +546,6 @@
       <color theme="9" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6"/>
-      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -535,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -602,15 +678,6 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -637,6 +704,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -651,6 +719,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -666,6 +735,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -680,6 +750,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -695,6 +766,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -709,6 +781,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -723,6 +796,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -737,6 +811,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -757,6 +832,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -776,6 +852,7 @@
         <sz val="11"/>
         <color theme="9" tint="0.39997558519241921"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -792,6 +869,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -806,6 +884,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -821,6 +900,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -845,6 +925,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -859,6 +940,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -873,6 +955,7 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -897,33 +980,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:F25" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A2D4003-659B-406D-8419-7901DC9093D7}" name="Tabela1" displayName="Tabela1" ref="A1:F23" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:F23" xr:uid="{5A2D4003-659B-406D-8419-7901DC9093D7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F23">
     <sortCondition ref="F1:F23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="beneficio_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="beneficio_nome" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="valor_unico" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="qtd_dias" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="valor_total" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sigla" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{7560D60F-D515-4115-971B-9293F6C0DEFA}" name="beneficio_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3069BA3D-9DD7-4E79-89A3-605AB8E313E1}" name="beneficio_nome" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{8B26F146-122B-4BDB-B1A4-4FC643A11BDC}" name="valor_unico" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{C7795B54-C132-4226-B8D4-332E111F45E8}" name="qtd_dias" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{43121516-66CE-4779-B5DA-3B959451298A}" name="valor_total" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{2C9268F3-6A40-40C7-8081-40A712D7A723}" name="sigla" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela15" displayName="Tabela15" ref="A1:F37" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DEF1EC70-4E43-4023-A9EB-B1F09A5595C2}" name="Tabela15" displayName="Tabela15" ref="A1:F34" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:F34" xr:uid="{DEF1EC70-4E43-4023-A9EB-B1F09A5595C2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="beneficio_id" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="beneficio_nome" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="tipoescala" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="funcao" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="posto" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="horas" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{2A83B647-6BF5-4814-B59D-4C77D83D847C}" name="beneficio_id" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{DFD8919E-0453-4BBF-BB24-1E04D3DC35A3}" name="beneficio_nome" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{4C4C0A80-8C67-4EFB-B9A0-0023A65C5A76}" name="tipoescala" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{79E448D2-4259-4CEC-9A46-DCCDEA0668FF}" name="funcao" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{260D29DD-2DDD-40E0-ACF3-74C28269347D}" name="posto" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{B7B16F7B-D7F0-4A76-8A9D-D57850D8F69F}" name="horas" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1245,9 +1328,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA7D0EF-9047-440C-B5CB-3A759BDC516E}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -1280,7 +1363,7 @@
         <v>16</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>11</v>
@@ -1306,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I2" s="7">
         <v>53</v>
@@ -1332,7 +1415,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I3" s="7">
         <v>51</v>
@@ -1346,19 +1429,19 @@
         <v>19</v>
       </c>
       <c r="C4" s="8">
-        <v>462.97</v>
+        <v>440</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="8">
-        <v>462.97</v>
+        <v>440</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I4" s="7">
         <v>41</v>
@@ -1366,80 +1449,80 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5" s="8">
-        <v>154.49</v>
+        <v>3.19</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="8">
-        <v>154.49</v>
+        <v>3.19</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I5" s="7">
-        <v>137</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="8">
-        <v>3.19</v>
+        <v>12.53</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="8">
-        <v>3.19</v>
+        <v>12.53</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I6" s="7">
-        <v>55</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8">
-        <v>12.53</v>
+        <v>154.49</v>
       </c>
       <c r="D7" s="9">
         <v>1</v>
       </c>
       <c r="E7" s="8">
-        <v>12.53</v>
+        <v>154.49</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I7" s="7">
-        <v>48</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1462,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1485,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1508,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1531,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1554,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1577,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1600,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1621,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1644,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1667,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1690,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1713,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1736,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1759,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1782,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1793,78 +1876,24 @@
         <v>38</v>
       </c>
       <c r="C23" s="8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D23" s="9">
         <v>22</v>
       </c>
       <c r="E23" s="8">
-        <v>968</v>
+        <v>924</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>58</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D24" s="9">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>59</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D25" s="9">
-        <v>1</v>
-      </c>
-      <c r="E25" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F28" s="9">
-        <f>E20*3.5%</f>
-        <v>18.379900000000003</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="F2:F25">
+  <conditionalFormatting sqref="F2:F23">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>"VA"</formula>
     </cfRule>
@@ -1877,7 +1906,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD0BFC1-A326-4EB9-ABAA-3187E5A0F759}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1905,7 +1934,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>5</v>
@@ -1920,10 +1949,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
@@ -1937,10 +1966,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1952,10 +1981,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1975,7 +2004,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2023,7 +2052,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="19" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -2056,17 +2085,17 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2075,9 +2104,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E04232E-BE05-481A-870B-2D7BAA50518B}">
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -2105,7 +2134,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2122,7 +2151,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>43</v>
@@ -2139,10 +2168,10 @@
         <v>43</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>43</v>
@@ -2158,11 +2187,11 @@
       <c r="C4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>50</v>
+      <c r="D4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>58</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>43</v>
@@ -2179,7 +2208,7 @@
         <v>43</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>43</v>
@@ -2198,7 +2227,7 @@
       <c r="C6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="15" t="s">
@@ -2222,144 +2251,144 @@
         <v>43</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>55</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="15" t="s">
+      <c r="A8" s="9">
+        <v>48</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <v>48</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>48</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="A10" s="9">
+        <v>137</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="11">
         <v>136</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>43</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11">
-        <v>136</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="A13" s="9">
+        <v>63</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>43</v>
@@ -2370,16 +2399,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>43</v>
@@ -2390,16 +2419,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>43</v>
@@ -2409,51 +2438,51 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9">
+      <c r="A17" s="11">
         <v>56</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="11">
-        <v>56</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="A18" s="9">
+        <v>54</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>43</v>
@@ -2461,330 +2490,304 @@
       <c r="D19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>51</v>
+      <c r="E19" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>56</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="11">
         <v>50</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="15" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11">
-        <v>50</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="9">
+        <v>49</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>43</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+        <v>54</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="F24" s="10" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="11">
+        <v>45</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="9">
+        <v>44</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="11">
+        <v>44</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="9">
+        <v>43</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>43</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>42</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>42</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>40</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="E33" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>40</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="11">
-        <v>45</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9">
-        <v>44</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="11">
-        <v>44</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>43</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="11">
-        <v>43</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
-        <v>42</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="11">
-        <v>42</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="9">
-        <v>40</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="11">
-        <v>40</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="9">
-        <v>58</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
-        <v>59</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="E34" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="15" t="s">
         <v>43</v>
       </c>
     </row>

--- a/data/BENEFICIOS - RELACAO.xlsx
+++ b/data/BENEFICIOS - RELACAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\06 - OUTROS\08 - APLICAÇÕES\IMPORTAR DADOS\Importar_Dados\DADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\NUCLEO\06 - OUTROS\08 - APLICAÇÕES\01 - IMPORTAR DADOS\01 - VERSÃO DESKTOP\Importar_Dados\DADOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E0B972-4921-4CBB-8292-652B92DF68B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573D2A27-D0CA-4EBE-9E6F-4F622ABFE78C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{73204379-9103-4EC7-9959-F9B57A8EF193}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BENEFICIOS" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="85">
   <si>
     <t>VA</t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>SUPERVISOR DE VIGILANCIA</t>
-  </si>
-  <si>
-    <t>INST.AMBIENTAL VALE</t>
   </si>
   <si>
     <t>INSTITUTO AMBIENTAL VALE</t>
@@ -270,44 +267,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>AMBIENTAL VALE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra)</t>
-    </r>
-  </si>
-  <si>
     <t>COZINHEIRO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="0.39997558519241921"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">AMBIENTAL VALE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(contém a palavra)</t>
-    </r>
   </si>
   <si>
     <t>AJUDANTE DE COZINHA</t>
@@ -334,36 +294,6 @@
     <t>4h</t>
   </si>
   <si>
-    <r>
-      <t>CESAN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra, não brasilia)</t>
-    </r>
-  </si>
-  <si>
     <t>SIM</t>
   </si>
   <si>
@@ -383,21 +313,6 @@
   </si>
   <si>
     <t>GUIDONI TB2 - 5X2</t>
-  </si>
-  <si>
-    <r>
-      <t>GUIDONI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra)</t>
-    </r>
   </si>
   <si>
     <t>motorista RECEBE (VA + CB)</t>
@@ -426,50 +341,6 @@
   <si>
     <t>EX:
 ESC 05X02 - 14:00 AS 18:00 (não tem almoço é 4h)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="0.39997558519241921"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (contém a palavra, não brasilia)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="9" tint="0.39997558519241921"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">CESAN </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(contém a palavra)</t>
-    </r>
   </si>
   <si>
     <t>6h</t>
@@ -489,12 +360,59 @@
       <t xml:space="preserve"> (contém a palavra)</t>
     </r>
   </si>
+  <si>
+    <t>VALE SA</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VT TRANSPORTE - GVBUS 1 P/DIA
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VT TRANSPORTE - GVBUS 2 P/DIA
+</t>
+  </si>
+  <si>
+    <r>
+      <t>CETURB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (contém a palavra)</t>
+    </r>
+  </si>
+  <si>
+    <t>SUPERVISOR(A)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MULTILIFT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(contém a palavra)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +464,12 @@
       <color theme="9" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -611,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -678,6 +602,15 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -704,7 +637,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -719,7 +651,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -735,7 +666,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -750,7 +680,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -766,7 +695,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -781,7 +709,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -796,7 +723,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -811,7 +737,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -832,7 +757,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -852,7 +776,6 @@
         <sz val="11"/>
         <color theme="9" tint="0.39997558519241921"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -869,7 +792,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -884,7 +806,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -900,7 +821,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -925,7 +845,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -940,7 +859,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -955,7 +873,6 @@
         <sz val="11"/>
         <color theme="6"/>
         <name val="Aptos Narrow"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
       <fill>
@@ -980,33 +897,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A2D4003-659B-406D-8419-7901DC9093D7}" name="Tabela1" displayName="Tabela1" ref="A1:F23" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:F23" xr:uid="{5A2D4003-659B-406D-8419-7901DC9093D7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:F25" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F23">
     <sortCondition ref="F1:F23"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{7560D60F-D515-4115-971B-9293F6C0DEFA}" name="beneficio_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3069BA3D-9DD7-4E79-89A3-605AB8E313E1}" name="beneficio_nome" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{8B26F146-122B-4BDB-B1A4-4FC643A11BDC}" name="valor_unico" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{C7795B54-C132-4226-B8D4-332E111F45E8}" name="qtd_dias" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{43121516-66CE-4779-B5DA-3B959451298A}" name="valor_total" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{2C9268F3-6A40-40C7-8081-40A712D7A723}" name="sigla" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="beneficio_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="beneficio_nome" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="valor_unico" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="qtd_dias" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="valor_total" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="sigla" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DEF1EC70-4E43-4023-A9EB-B1F09A5595C2}" name="Tabela15" displayName="Tabela15" ref="A1:F34" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:F34" xr:uid="{DEF1EC70-4E43-4023-A9EB-B1F09A5595C2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela15" displayName="Tabela15" ref="A1:F37" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:F37" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2A83B647-6BF5-4814-B59D-4C77D83D847C}" name="beneficio_id" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{DFD8919E-0453-4BBF-BB24-1E04D3DC35A3}" name="beneficio_nome" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{4C4C0A80-8C67-4EFB-B9A0-0023A65C5A76}" name="tipoescala" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{79E448D2-4259-4CEC-9A46-DCCDEA0668FF}" name="funcao" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{260D29DD-2DDD-40E0-ACF3-74C28269347D}" name="posto" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{B7B16F7B-D7F0-4A76-8A9D-D57850D8F69F}" name="horas" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="beneficio_id" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="beneficio_nome" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="tipoescala" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="funcao" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="posto" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="horas" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1328,9 +1245,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BA7D0EF-9047-440C-B5CB-3A759BDC516E}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -1363,7 +1280,7 @@
         <v>16</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>11</v>
@@ -1389,7 +1306,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I2" s="7">
         <v>53</v>
@@ -1415,7 +1332,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I3" s="7">
         <v>51</v>
@@ -1429,19 +1346,19 @@
         <v>19</v>
       </c>
       <c r="C4" s="8">
-        <v>440</v>
+        <v>462.97</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="8">
-        <v>440</v>
+        <v>462.97</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I4" s="7">
         <v>41</v>
@@ -1449,80 +1366,80 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8">
-        <v>3.19</v>
+        <v>154.49</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="8">
-        <v>3.19</v>
+        <v>154.49</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I5" s="7">
-        <v>55</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8">
-        <v>12.53</v>
+        <v>3.19</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="8">
-        <v>12.53</v>
+        <v>3.19</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I6" s="7">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="8">
-        <v>154.49</v>
+        <v>12.53</v>
       </c>
       <c r="D7" s="9">
         <v>1</v>
       </c>
       <c r="E7" s="8">
-        <v>154.49</v>
+        <v>12.53</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I7" s="7">
-        <v>137</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1545,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1568,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1591,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1614,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1637,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1660,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1683,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1704,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1727,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1750,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1773,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1796,7 +1713,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1819,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1842,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1865,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1876,24 +1793,78 @@
         <v>38</v>
       </c>
       <c r="C23" s="8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D23" s="9">
         <v>22</v>
       </c>
       <c r="E23" s="8">
-        <v>924</v>
+        <v>968</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>58</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D24" s="9">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>59</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D25" s="9">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F28" s="9">
+        <f>E20*3.5%</f>
+        <v>18.379900000000003</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="F2:F23">
+  <conditionalFormatting sqref="F2:F25">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>"VA"</formula>
     </cfRule>
@@ -1906,7 +1877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD0BFC1-A326-4EB9-ABAA-3187E5A0F759}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1934,7 +1905,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>5</v>
@@ -1949,10 +1920,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
@@ -1966,10 +1937,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1981,10 +1952,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -2004,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -2052,7 +2023,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="19" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -2085,17 +2056,17 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2104,9 +2075,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E04232E-BE05-481A-870B-2D7BAA50518B}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.28515625" style="7" bestFit="1" customWidth="1"/>
@@ -2134,7 +2105,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,7 +2122,7 @@
         <v>43</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>43</v>
@@ -2168,10 +2139,10 @@
         <v>43</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>43</v>
@@ -2187,11 +2158,11 @@
       <c r="C4" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>58</v>
+      <c r="D4" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>50</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>43</v>
@@ -2208,7 +2179,7 @@
         <v>43</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>43</v>
@@ -2227,7 +2198,7 @@
       <c r="C6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="15" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="15" t="s">
@@ -2251,144 +2222,144 @@
         <v>43</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9">
+      <c r="A8" s="11">
+        <v>55</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
         <v>48</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="C9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
+      <c r="E9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
         <v>48</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
-        <v>137</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
+        <v>137</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
         <v>136</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B12" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
+      <c r="C12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
         <v>136</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B13" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>63</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="10" t="s">
+      <c r="C13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>43</v>
@@ -2399,16 +2370,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>43</v>
@@ -2419,375 +2390,401 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
+        <v>57</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="9">
         <v>56</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="11">
+      <c r="C17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
         <v>56</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B18" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9">
-        <v>54</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="E18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
+        <v>54</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="9">
         <v>52</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B20" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E19" s="18" t="s">
+      <c r="C20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9">
+        <v>50</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+      <c r="E21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="F21" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>50</v>
+      </c>
+      <c r="B22" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="C22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="E22" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
-        <v>49</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
+        <v>31</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>43</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
       <c r="F24" s="10" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
+        <v>46</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="9">
         <v>45</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B26" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
         <v>45</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B27" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="9">
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="9">
         <v>44</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C28" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="11">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="11">
         <v>44</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B29" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C29" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9">
-        <v>43</v>
-      </c>
-      <c r="B29" s="13" t="s">
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="9">
+        <v>43</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C30" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="11">
-        <v>43</v>
-      </c>
-      <c r="B30" s="14" t="s">
+      <c r="D30" s="10"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>43</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C31" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
+      <c r="D31" s="15"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="9">
         <v>42</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B32" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C32" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E31" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="11">
+      <c r="D32" s="10"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
         <v>42</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B33" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C33" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E32" s="21" t="s">
+      <c r="D33" s="15"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="9">
+        <v>40</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="11">
+        <v>40</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="9">
+        <v>58</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
-        <v>40</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="11">
-        <v>40</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="15" t="s">
+      <c r="F36" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="9">
+        <v>59</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>43</v>
       </c>
     </row>
